--- a/partner_results/imr/ClassMissingEnglishDefinition_imr.xlsx
+++ b/partner_results/imr/ClassMissingEnglishDefinition_imr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,11 +434,6 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>Add English definition</t>
         </is>
       </c>
@@ -456,7 +451,6 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,7 +465,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
